--- a/evaluation/multiple_choice_qa/MMLU_Anatomy/qwen2.5_trained/fa_qwn_result.xlsx
+++ b/evaluation/multiple_choice_qa/MMLU_Anatomy/qwen2.5_trained/fa_qwn_result.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A60FDFBE-461E-4850-B836-B0332F052EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D4FBC45-3427-463B-8696-E4A3FCE0ED6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="550">
   <si>
     <t>Question</t>
   </si>
@@ -1807,9 +1807,6 @@
   </si>
   <si>
     <t>معاینه بیماری استرابیسم جهت دار داخلی نشان می‌دهد که عصبی مورد نظر عصب چشمی حرکتی است. در این نوع استرابیسم، عصب چشمی حرکتی آسیب می‌پذیرد و ناشی از آن توجه چشم به جهت خارجی کاهش یافته و توجه به جهت داخلی افزایش یافته است.</t>
-  </si>
-  <si>
-    <t>invalid</t>
   </si>
   <si>
     <t>زمانی که بیمار از شیشه قدی می افتد، عصب حرکتی محیطی مچ دستش قطع می شود. اگر عصب بازسازی نشود، پس از حدود 6 ماه ماهیچه هایی که به طور معمول عصب می کنند، علائم کدام یک از چهار گزینه زیر را نشان می دهند؟</t>
@@ -5080,24 +5077,24 @@
         <v>309</v>
       </c>
       <c r="F76" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
+        <v>310</v>
+      </c>
+      <c r="B77" t="s">
         <v>311</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" t="s">
         <v>312</v>
       </c>
-      <c r="C77" t="s">
-        <v>23</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>313</v>
-      </c>
-      <c r="E77" t="s">
-        <v>314</v>
       </c>
       <c r="F77" t="s">
         <v>23</v>
@@ -5105,19 +5102,19 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
+        <v>314</v>
+      </c>
+      <c r="B78" t="s">
         <v>315</v>
-      </c>
-      <c r="B78" t="s">
-        <v>316</v>
       </c>
       <c r="C78" t="s">
         <v>8</v>
       </c>
       <c r="D78" t="s">
+        <v>316</v>
+      </c>
+      <c r="E78" t="s">
         <v>317</v>
-      </c>
-      <c r="E78" t="s">
-        <v>318</v>
       </c>
       <c r="F78" t="s">
         <v>8</v>
@@ -5125,19 +5122,19 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
+        <v>318</v>
+      </c>
+      <c r="B79" t="s">
         <v>319</v>
-      </c>
-      <c r="B79" t="s">
-        <v>320</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
       </c>
       <c r="D79" t="s">
+        <v>320</v>
+      </c>
+      <c r="E79" t="s">
         <v>321</v>
-      </c>
-      <c r="E79" t="s">
-        <v>322</v>
       </c>
       <c r="F79" t="s">
         <v>11</v>
@@ -5145,19 +5142,19 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
+        <v>322</v>
+      </c>
+      <c r="B80" t="s">
         <v>323</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80" t="s">
         <v>324</v>
       </c>
-      <c r="C80" t="s">
-        <v>23</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>325</v>
-      </c>
-      <c r="E80" t="s">
-        <v>326</v>
       </c>
       <c r="F80" t="s">
         <v>23</v>
@@ -5165,19 +5162,19 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
+        <v>326</v>
+      </c>
+      <c r="B81" t="s">
         <v>327</v>
-      </c>
-      <c r="B81" t="s">
-        <v>328</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
       </c>
       <c r="D81" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" t="s">
         <v>329</v>
-      </c>
-      <c r="E81" t="s">
-        <v>330</v>
       </c>
       <c r="F81" t="s">
         <v>11</v>
@@ -5185,19 +5182,19 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
+        <v>330</v>
+      </c>
+      <c r="B82" t="s">
         <v>331</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" t="s">
         <v>332</v>
       </c>
-      <c r="C82" t="s">
-        <v>11</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>333</v>
-      </c>
-      <c r="E82" t="s">
-        <v>334</v>
       </c>
       <c r="F82" t="s">
         <v>11</v>
@@ -5205,19 +5202,19 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
+        <v>334</v>
+      </c>
+      <c r="B83" t="s">
         <v>335</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" t="s">
         <v>336</v>
       </c>
-      <c r="C83" t="s">
-        <v>11</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>337</v>
-      </c>
-      <c r="E83" t="s">
-        <v>338</v>
       </c>
       <c r="F83" t="s">
         <v>23</v>
@@ -5225,19 +5222,19 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
+        <v>338</v>
+      </c>
+      <c r="B84" t="s">
         <v>339</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" t="s">
         <v>340</v>
       </c>
-      <c r="C84" t="s">
-        <v>23</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>341</v>
-      </c>
-      <c r="E84" t="s">
-        <v>342</v>
       </c>
       <c r="F84" t="s">
         <v>20</v>
@@ -5245,19 +5242,19 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
+        <v>342</v>
+      </c>
+      <c r="B85" t="s">
         <v>343</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" t="s">
         <v>344</v>
       </c>
-      <c r="C85" t="s">
-        <v>11</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>345</v>
-      </c>
-      <c r="E85" t="s">
-        <v>346</v>
       </c>
       <c r="F85" t="s">
         <v>20</v>
@@ -5265,19 +5262,19 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
+        <v>346</v>
+      </c>
+      <c r="B86" t="s">
         <v>347</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="s">
         <v>348</v>
       </c>
-      <c r="C86" t="s">
-        <v>11</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>349</v>
-      </c>
-      <c r="E86" t="s">
-        <v>350</v>
       </c>
       <c r="F86" t="s">
         <v>8</v>
@@ -5285,19 +5282,19 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
+        <v>350</v>
+      </c>
+      <c r="B87" t="s">
         <v>351</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
         <v>352</v>
       </c>
-      <c r="C87" t="s">
-        <v>23</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>353</v>
-      </c>
-      <c r="E87" t="s">
-        <v>354</v>
       </c>
       <c r="F87" t="s">
         <v>23</v>
@@ -5305,19 +5302,19 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
+        <v>354</v>
+      </c>
+      <c r="B88" t="s">
         <v>355</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" t="s">
         <v>356</v>
       </c>
-      <c r="C88" t="s">
-        <v>23</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>357</v>
-      </c>
-      <c r="E88" t="s">
-        <v>358</v>
       </c>
       <c r="F88" t="s">
         <v>11</v>
@@ -5325,19 +5322,19 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
+        <v>358</v>
+      </c>
+      <c r="B89" t="s">
         <v>359</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" t="s">
         <v>360</v>
       </c>
-      <c r="C89" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>361</v>
-      </c>
-      <c r="E89" t="s">
-        <v>362</v>
       </c>
       <c r="F89" t="s">
         <v>23</v>
@@ -5345,19 +5342,19 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
+        <v>362</v>
+      </c>
+      <c r="B90" t="s">
         <v>363</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" t="s">
         <v>364</v>
       </c>
-      <c r="C90" t="s">
-        <v>23</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>365</v>
-      </c>
-      <c r="E90" t="s">
-        <v>366</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
@@ -5365,19 +5362,19 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
+        <v>366</v>
+      </c>
+      <c r="B91" t="s">
         <v>367</v>
-      </c>
-      <c r="B91" t="s">
-        <v>368</v>
       </c>
       <c r="C91" t="s">
         <v>8</v>
       </c>
       <c r="D91" t="s">
+        <v>368</v>
+      </c>
+      <c r="E91" t="s">
         <v>369</v>
-      </c>
-      <c r="E91" t="s">
-        <v>370</v>
       </c>
       <c r="F91" t="s">
         <v>8</v>
@@ -5385,19 +5382,19 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
+        <v>370</v>
+      </c>
+      <c r="B92" t="s">
         <v>371</v>
-      </c>
-      <c r="B92" t="s">
-        <v>372</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
       </c>
       <c r="D92" t="s">
+        <v>372</v>
+      </c>
+      <c r="E92" t="s">
         <v>373</v>
-      </c>
-      <c r="E92" t="s">
-        <v>374</v>
       </c>
       <c r="F92" t="s">
         <v>20</v>
@@ -5405,19 +5402,19 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
+        <v>374</v>
+      </c>
+      <c r="B93" t="s">
         <v>375</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" t="s">
         <v>376</v>
       </c>
-      <c r="C93" t="s">
-        <v>11</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>377</v>
-      </c>
-      <c r="E93" t="s">
-        <v>378</v>
       </c>
       <c r="F93" t="s">
         <v>20</v>
@@ -5425,19 +5422,19 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
+        <v>378</v>
+      </c>
+      <c r="B94" t="s">
         <v>379</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" t="s">
         <v>380</v>
       </c>
-      <c r="C94" t="s">
-        <v>11</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>381</v>
-      </c>
-      <c r="E94" t="s">
-        <v>382</v>
       </c>
       <c r="F94" t="s">
         <v>11</v>
@@ -5445,19 +5442,19 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
+        <v>382</v>
+      </c>
+      <c r="B95" t="s">
         <v>383</v>
-      </c>
-      <c r="B95" t="s">
-        <v>384</v>
       </c>
       <c r="C95" t="s">
         <v>20</v>
       </c>
       <c r="D95" t="s">
+        <v>384</v>
+      </c>
+      <c r="E95" t="s">
         <v>385</v>
-      </c>
-      <c r="E95" t="s">
-        <v>386</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
@@ -5465,19 +5462,19 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
+        <v>386</v>
+      </c>
+      <c r="B96" t="s">
         <v>387</v>
-      </c>
-      <c r="B96" t="s">
-        <v>388</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
       </c>
       <c r="D96" t="s">
+        <v>388</v>
+      </c>
+      <c r="E96" t="s">
         <v>389</v>
-      </c>
-      <c r="E96" t="s">
-        <v>390</v>
       </c>
       <c r="F96" t="s">
         <v>11</v>
@@ -5485,19 +5482,19 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
+        <v>390</v>
+      </c>
+      <c r="B97" t="s">
         <v>391</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
+        <v>23</v>
+      </c>
+      <c r="D97" t="s">
         <v>392</v>
       </c>
-      <c r="C97" t="s">
-        <v>23</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>393</v>
-      </c>
-      <c r="E97" t="s">
-        <v>394</v>
       </c>
       <c r="F97" t="s">
         <v>11</v>
@@ -5505,19 +5502,19 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
+        <v>394</v>
+      </c>
+      <c r="B98" t="s">
         <v>395</v>
-      </c>
-      <c r="B98" t="s">
-        <v>396</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
       </c>
       <c r="D98" t="s">
+        <v>396</v>
+      </c>
+      <c r="E98" t="s">
         <v>397</v>
-      </c>
-      <c r="E98" t="s">
-        <v>398</v>
       </c>
       <c r="F98" t="s">
         <v>23</v>
@@ -5525,19 +5522,19 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
+        <v>398</v>
+      </c>
+      <c r="B99" t="s">
         <v>399</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>23</v>
+      </c>
+      <c r="D99" t="s">
         <v>400</v>
       </c>
-      <c r="C99" t="s">
-        <v>23</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>401</v>
-      </c>
-      <c r="E99" t="s">
-        <v>402</v>
       </c>
       <c r="F99" t="s">
         <v>11</v>
@@ -5545,19 +5542,19 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
+        <v>402</v>
+      </c>
+      <c r="B100" t="s">
         <v>403</v>
-      </c>
-      <c r="B100" t="s">
-        <v>404</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
       </c>
       <c r="D100" t="s">
+        <v>404</v>
+      </c>
+      <c r="E100" t="s">
         <v>405</v>
-      </c>
-      <c r="E100" t="s">
-        <v>406</v>
       </c>
       <c r="F100" t="s">
         <v>20</v>
@@ -5565,19 +5562,19 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
+        <v>406</v>
+      </c>
+      <c r="B101" t="s">
         <v>407</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" t="s">
         <v>408</v>
       </c>
-      <c r="C101" t="s">
-        <v>23</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>409</v>
-      </c>
-      <c r="E101" t="s">
-        <v>410</v>
       </c>
       <c r="F101" t="s">
         <v>11</v>
@@ -5585,19 +5582,19 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
+        <v>410</v>
+      </c>
+      <c r="B102" t="s">
         <v>411</v>
-      </c>
-      <c r="B102" t="s">
-        <v>412</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
+        <v>412</v>
+      </c>
+      <c r="E102" t="s">
         <v>413</v>
-      </c>
-      <c r="E102" t="s">
-        <v>414</v>
       </c>
       <c r="F102" t="s">
         <v>8</v>
@@ -5605,19 +5602,19 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
+        <v>414</v>
+      </c>
+      <c r="B103" t="s">
         <v>415</v>
-      </c>
-      <c r="B103" t="s">
-        <v>416</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
       </c>
       <c r="D103" t="s">
+        <v>416</v>
+      </c>
+      <c r="E103" t="s">
         <v>417</v>
-      </c>
-      <c r="E103" t="s">
-        <v>418</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -5625,19 +5622,19 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
+        <v>418</v>
+      </c>
+      <c r="B104" t="s">
         <v>419</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
+        <v>23</v>
+      </c>
+      <c r="D104" t="s">
         <v>420</v>
       </c>
-      <c r="C104" t="s">
-        <v>23</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>421</v>
-      </c>
-      <c r="E104" t="s">
-        <v>422</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
@@ -5645,19 +5642,19 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
+        <v>422</v>
+      </c>
+      <c r="B105" t="s">
         <v>423</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" t="s">
         <v>424</v>
       </c>
-      <c r="C105" t="s">
-        <v>11</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>425</v>
-      </c>
-      <c r="E105" t="s">
-        <v>426</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -5665,19 +5662,19 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
+        <v>426</v>
+      </c>
+      <c r="B106" t="s">
         <v>427</v>
-      </c>
-      <c r="B106" t="s">
-        <v>428</v>
       </c>
       <c r="C106" t="s">
         <v>8</v>
       </c>
       <c r="D106" t="s">
+        <v>428</v>
+      </c>
+      <c r="E106" t="s">
         <v>429</v>
-      </c>
-      <c r="E106" t="s">
-        <v>430</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
@@ -5685,19 +5682,19 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
+        <v>430</v>
+      </c>
+      <c r="B107" t="s">
         <v>431</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" t="s">
         <v>432</v>
       </c>
-      <c r="C107" t="s">
-        <v>23</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>433</v>
-      </c>
-      <c r="E107" t="s">
-        <v>434</v>
       </c>
       <c r="F107" t="s">
         <v>23</v>
@@ -5705,19 +5702,19 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
+        <v>434</v>
+      </c>
+      <c r="B108" t="s">
         <v>435</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" t="s">
         <v>436</v>
       </c>
-      <c r="C108" t="s">
-        <v>23</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>437</v>
-      </c>
-      <c r="E108" t="s">
-        <v>438</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
@@ -5725,19 +5722,19 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
+        <v>438</v>
+      </c>
+      <c r="B109" t="s">
         <v>439</v>
-      </c>
-      <c r="B109" t="s">
-        <v>440</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
       </c>
       <c r="D109" t="s">
+        <v>440</v>
+      </c>
+      <c r="E109" t="s">
         <v>441</v>
-      </c>
-      <c r="E109" t="s">
-        <v>442</v>
       </c>
       <c r="F109" t="s">
         <v>11</v>
@@ -5745,19 +5742,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
+        <v>442</v>
+      </c>
+      <c r="B110" t="s">
         <v>443</v>
-      </c>
-      <c r="B110" t="s">
-        <v>444</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
       </c>
       <c r="D110" t="s">
+        <v>444</v>
+      </c>
+      <c r="E110" t="s">
         <v>445</v>
-      </c>
-      <c r="E110" t="s">
-        <v>446</v>
       </c>
       <c r="F110" t="s">
         <v>20</v>
@@ -5765,19 +5762,19 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
+        <v>446</v>
+      </c>
+      <c r="B111" t="s">
         <v>447</v>
-      </c>
-      <c r="B111" t="s">
-        <v>448</v>
       </c>
       <c r="C111" t="s">
         <v>8</v>
       </c>
       <c r="D111" t="s">
+        <v>448</v>
+      </c>
+      <c r="E111" t="s">
         <v>449</v>
-      </c>
-      <c r="E111" t="s">
-        <v>450</v>
       </c>
       <c r="F111" t="s">
         <v>8</v>
@@ -5785,19 +5782,19 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
+        <v>450</v>
+      </c>
+      <c r="B112" t="s">
         <v>451</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
+        <v>23</v>
+      </c>
+      <c r="D112" t="s">
         <v>452</v>
       </c>
-      <c r="C112" t="s">
-        <v>23</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>453</v>
-      </c>
-      <c r="E112" t="s">
-        <v>454</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -5805,19 +5802,19 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
+        <v>454</v>
+      </c>
+      <c r="B113" t="s">
         <v>455</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
+        <v>23</v>
+      </c>
+      <c r="D113" t="s">
         <v>456</v>
       </c>
-      <c r="C113" t="s">
-        <v>23</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>457</v>
-      </c>
-      <c r="E113" t="s">
-        <v>458</v>
       </c>
       <c r="F113" t="s">
         <v>23</v>
@@ -5825,19 +5822,19 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
+        <v>458</v>
+      </c>
+      <c r="B114" t="s">
         <v>459</v>
-      </c>
-      <c r="B114" t="s">
-        <v>460</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
+        <v>460</v>
+      </c>
+      <c r="E114" t="s">
         <v>461</v>
-      </c>
-      <c r="E114" t="s">
-        <v>462</v>
       </c>
       <c r="F114" t="s">
         <v>20</v>
@@ -5845,19 +5842,19 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
+        <v>462</v>
+      </c>
+      <c r="B115" t="s">
         <v>463</v>
-      </c>
-      <c r="B115" t="s">
-        <v>464</v>
       </c>
       <c r="C115" t="s">
         <v>8</v>
       </c>
       <c r="D115" t="s">
+        <v>464</v>
+      </c>
+      <c r="E115" t="s">
         <v>465</v>
-      </c>
-      <c r="E115" t="s">
-        <v>466</v>
       </c>
       <c r="F115" t="s">
         <v>23</v>
@@ -5865,19 +5862,19 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
+        <v>466</v>
+      </c>
+      <c r="B116" t="s">
         <v>467</v>
-      </c>
-      <c r="B116" t="s">
-        <v>468</v>
       </c>
       <c r="C116" t="s">
         <v>8</v>
       </c>
       <c r="D116" t="s">
+        <v>468</v>
+      </c>
+      <c r="E116" t="s">
         <v>469</v>
-      </c>
-      <c r="E116" t="s">
-        <v>470</v>
       </c>
       <c r="F116" t="s">
         <v>23</v>
@@ -5885,19 +5882,19 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
+        <v>470</v>
+      </c>
+      <c r="B117" t="s">
         <v>471</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" t="s">
         <v>472</v>
       </c>
-      <c r="C117" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>473</v>
-      </c>
-      <c r="E117" t="s">
-        <v>474</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
@@ -5905,19 +5902,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
+        <v>474</v>
+      </c>
+      <c r="B118" t="s">
         <v>475</v>
-      </c>
-      <c r="B118" t="s">
-        <v>476</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
       </c>
       <c r="D118" t="s">
+        <v>476</v>
+      </c>
+      <c r="E118" t="s">
         <v>477</v>
-      </c>
-      <c r="E118" t="s">
-        <v>478</v>
       </c>
       <c r="F118" t="s">
         <v>20</v>
@@ -5925,19 +5922,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
+        <v>478</v>
+      </c>
+      <c r="B119" t="s">
         <v>479</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" t="s">
         <v>480</v>
       </c>
-      <c r="C119" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>481</v>
-      </c>
-      <c r="E119" t="s">
-        <v>482</v>
       </c>
       <c r="F119" t="s">
         <v>11</v>
@@ -5945,19 +5942,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
+        <v>482</v>
+      </c>
+      <c r="B120" t="s">
         <v>483</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" t="s">
         <v>484</v>
       </c>
-      <c r="C120" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>485</v>
-      </c>
-      <c r="E120" t="s">
-        <v>486</v>
       </c>
       <c r="F120" t="s">
         <v>20</v>
@@ -5965,19 +5962,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
+        <v>486</v>
+      </c>
+      <c r="B121" t="s">
         <v>487</v>
-      </c>
-      <c r="B121" t="s">
-        <v>488</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
       </c>
       <c r="D121" t="s">
+        <v>488</v>
+      </c>
+      <c r="E121" t="s">
         <v>489</v>
-      </c>
-      <c r="E121" t="s">
-        <v>490</v>
       </c>
       <c r="F121" t="s">
         <v>11</v>
@@ -5985,39 +5982,39 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
+        <v>490</v>
+      </c>
+      <c r="B122" t="s">
         <v>491</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
+        <v>23</v>
+      </c>
+      <c r="D122" t="s">
         <v>492</v>
       </c>
-      <c r="C122" t="s">
-        <v>23</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>493</v>
       </c>
-      <c r="E122" t="s">
-        <v>494</v>
-      </c>
       <c r="F122" t="s">
-        <v>310</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
+        <v>494</v>
+      </c>
+      <c r="B123" t="s">
         <v>495</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" t="s">
         <v>496</v>
       </c>
-      <c r="C123" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>497</v>
-      </c>
-      <c r="E123" t="s">
-        <v>498</v>
       </c>
       <c r="F123" t="s">
         <v>11</v>
@@ -6025,19 +6022,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
+        <v>498</v>
+      </c>
+      <c r="B124" t="s">
         <v>499</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
+        <v>23</v>
+      </c>
+      <c r="D124" t="s">
         <v>500</v>
       </c>
-      <c r="C124" t="s">
-        <v>23</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>501</v>
-      </c>
-      <c r="E124" t="s">
-        <v>502</v>
       </c>
       <c r="F124" t="s">
         <v>23</v>
@@ -6045,19 +6042,19 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
+        <v>502</v>
+      </c>
+      <c r="B125" t="s">
         <v>503</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" t="s">
         <v>504</v>
       </c>
-      <c r="C125" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>505</v>
-      </c>
-      <c r="E125" t="s">
-        <v>506</v>
       </c>
       <c r="F125" t="s">
         <v>11</v>
@@ -6065,19 +6062,19 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
+        <v>506</v>
+      </c>
+      <c r="B126" t="s">
         <v>507</v>
-      </c>
-      <c r="B126" t="s">
-        <v>508</v>
       </c>
       <c r="C126" t="s">
         <v>20</v>
       </c>
       <c r="D126" t="s">
+        <v>508</v>
+      </c>
+      <c r="E126" t="s">
         <v>509</v>
-      </c>
-      <c r="E126" t="s">
-        <v>510</v>
       </c>
       <c r="F126" t="s">
         <v>23</v>
@@ -6085,19 +6082,19 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
+        <v>510</v>
+      </c>
+      <c r="B127" t="s">
         <v>511</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" t="s">
         <v>512</v>
       </c>
-      <c r="C127" t="s">
-        <v>11</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>513</v>
-      </c>
-      <c r="E127" t="s">
-        <v>514</v>
       </c>
       <c r="F127" t="s">
         <v>20</v>
@@ -6105,19 +6102,19 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
+        <v>514</v>
+      </c>
+      <c r="B128" t="s">
         <v>515</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
+        <v>23</v>
+      </c>
+      <c r="D128" t="s">
         <v>516</v>
       </c>
-      <c r="C128" t="s">
-        <v>23</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>517</v>
-      </c>
-      <c r="E128" t="s">
-        <v>518</v>
       </c>
       <c r="F128" t="s">
         <v>23</v>
@@ -6125,19 +6122,19 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
+        <v>518</v>
+      </c>
+      <c r="B129" t="s">
         <v>519</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
+        <v>23</v>
+      </c>
+      <c r="D129" t="s">
         <v>520</v>
       </c>
-      <c r="C129" t="s">
-        <v>23</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
         <v>521</v>
-      </c>
-      <c r="E129" t="s">
-        <v>522</v>
       </c>
       <c r="F129" t="s">
         <v>11</v>
@@ -6145,19 +6142,19 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
+        <v>522</v>
+      </c>
+      <c r="B130" t="s">
         <v>523</v>
-      </c>
-      <c r="B130" t="s">
-        <v>524</v>
       </c>
       <c r="C130" t="s">
         <v>8</v>
       </c>
       <c r="D130" t="s">
+        <v>524</v>
+      </c>
+      <c r="E130" t="s">
         <v>525</v>
-      </c>
-      <c r="E130" t="s">
-        <v>526</v>
       </c>
       <c r="F130" t="s">
         <v>11</v>
@@ -6165,19 +6162,19 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
+        <v>526</v>
+      </c>
+      <c r="B131" t="s">
         <v>527</v>
-      </c>
-      <c r="B131" t="s">
-        <v>528</v>
       </c>
       <c r="C131" t="s">
         <v>8</v>
       </c>
       <c r="D131" t="s">
+        <v>528</v>
+      </c>
+      <c r="E131" t="s">
         <v>529</v>
-      </c>
-      <c r="E131" t="s">
-        <v>530</v>
       </c>
       <c r="F131" t="s">
         <v>11</v>
@@ -6185,19 +6182,19 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
+        <v>530</v>
+      </c>
+      <c r="B132" t="s">
         <v>531</v>
-      </c>
-      <c r="B132" t="s">
-        <v>532</v>
       </c>
       <c r="C132" t="s">
         <v>8</v>
       </c>
       <c r="D132" t="s">
+        <v>532</v>
+      </c>
+      <c r="E132" t="s">
         <v>533</v>
-      </c>
-      <c r="E132" t="s">
-        <v>534</v>
       </c>
       <c r="F132" t="s">
         <v>11</v>
@@ -6205,19 +6202,19 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
+        <v>534</v>
+      </c>
+      <c r="B133" t="s">
         <v>535</v>
-      </c>
-      <c r="B133" t="s">
-        <v>536</v>
       </c>
       <c r="C133" t="s">
         <v>20</v>
       </c>
       <c r="D133" t="s">
+        <v>536</v>
+      </c>
+      <c r="E133" t="s">
         <v>537</v>
-      </c>
-      <c r="E133" t="s">
-        <v>538</v>
       </c>
       <c r="F133" t="s">
         <v>20</v>
@@ -6225,19 +6222,19 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
+        <v>538</v>
+      </c>
+      <c r="B134" t="s">
         <v>539</v>
-      </c>
-      <c r="B134" t="s">
-        <v>540</v>
       </c>
       <c r="C134" t="s">
         <v>8</v>
       </c>
       <c r="D134" t="s">
+        <v>540</v>
+      </c>
+      <c r="E134" t="s">
         <v>541</v>
-      </c>
-      <c r="E134" t="s">
-        <v>542</v>
       </c>
       <c r="F134" t="s">
         <v>8</v>
@@ -6245,19 +6242,19 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
+        <v>542</v>
+      </c>
+      <c r="B135" t="s">
         <v>543</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
+        <v>23</v>
+      </c>
+      <c r="D135" t="s">
         <v>544</v>
       </c>
-      <c r="C135" t="s">
-        <v>23</v>
-      </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>545</v>
-      </c>
-      <c r="E135" t="s">
-        <v>546</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -6265,19 +6262,19 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
+        <v>546</v>
+      </c>
+      <c r="B136" t="s">
         <v>547</v>
-      </c>
-      <c r="B136" t="s">
-        <v>548</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
       </c>
       <c r="D136" t="s">
+        <v>548</v>
+      </c>
+      <c r="E136" t="s">
         <v>549</v>
-      </c>
-      <c r="E136" t="s">
-        <v>550</v>
       </c>
       <c r="F136" t="s">
         <v>23</v>

--- a/evaluation/multiple_choice_qa/MMLU_Anatomy/qwen2.5_trained/fa_qwn_result.xlsx
+++ b/evaluation/multiple_choice_qa/MMLU_Anatomy/qwen2.5_trained/fa_qwn_result.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D4FBC45-3427-463B-8696-E4A3FCE0ED6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21278347-0285-4773-8070-E73045ADA091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6097,7 +6097,7 @@
         <v>513</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -6137,7 +6137,7 @@
         <v>521</v>
       </c>
       <c r="F129" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:6">

--- a/evaluation/multiple_choice_qa/MMLU_Anatomy/qwen2.5_trained/fa_qwn_result.xlsx
+++ b/evaluation/multiple_choice_qa/MMLU_Anatomy/qwen2.5_trained/fa_qwn_result.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21278347-0285-4773-8070-E73045ADA091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77CAC1B3-D466-4F57-8D9F-5F3CFDF6AFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="551">
   <si>
     <t>Question</t>
   </si>
@@ -1011,6 +1011,9 @@
   <si>
     <t>شرایطی که در اختیار شما آورده شده، برای نارسایی اسفنکتر مری مربوط نمی‌شود. اسفنکتر مری در سمت راست گوارش مری قرار دارد و در حالت نارسی، علائمی مانند خستگی، ضعف، تغییرات در کارایی گوارش مری، و در برخی مواقع نارساییهای غیرمنتظره مانند نارسایی اسفنکتر مری می‌تواند مشاهده شود. 
 بنابراین، در مورد گزینه‌های ارائه شده، نارسایی اسفنکتر مری معمولاً ناشی از عللی است که موجب نارسایی اسفنکتر مری می‌شود، و نه این علل‌ها خود که شامل بیماری کرون (گزینه A)، واریس مری (گزینه B)، بیماری بازگشت اسید به مری (گزینه C) و تنگی پیلور (گزینه D) می‌باشد.</t>
+  </si>
+  <si>
+    <t>invalid</t>
   </si>
   <si>
     <t>ماهیچه های کام نرم توسط شاخه هایی از... عصب دهی می شوند</t>
@@ -4397,24 +4400,24 @@
         <v>173</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C43" t="s">
         <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E43" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F43" t="s">
         <v>8</v>
@@ -4422,19 +4425,19 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B44" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F44" t="s">
         <v>20</v>
@@ -4442,19 +4445,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C45" t="s">
         <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E45" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F45" t="s">
         <v>23</v>
@@ -4462,19 +4465,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F46" t="s">
         <v>23</v>
@@ -4482,19 +4485,19 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C47" t="s">
         <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F47" t="s">
         <v>8</v>
@@ -4502,19 +4505,19 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F48" t="s">
         <v>8</v>
@@ -4522,19 +4525,19 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C49" t="s">
         <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F49" t="s">
         <v>23</v>
@@ -4542,19 +4545,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F50" t="s">
         <v>23</v>
@@ -4562,19 +4565,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C51" t="s">
         <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E51" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F51" t="s">
         <v>23</v>
@@ -4582,19 +4585,19 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
         <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E52" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F52" t="s">
         <v>23</v>
@@ -4602,19 +4605,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C53" t="s">
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E53" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F53" t="s">
         <v>8</v>
@@ -4622,19 +4625,19 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E54" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F54" t="s">
         <v>8</v>
@@ -4642,19 +4645,19 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E55" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
@@ -4662,19 +4665,19 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
       </c>
       <c r="D56" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E56" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
@@ -4682,19 +4685,19 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E57" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F57" t="s">
         <v>8</v>
@@ -4702,19 +4705,19 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E58" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F58" t="s">
         <v>8</v>
@@ -4722,19 +4725,19 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B59" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C59" t="s">
         <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F59" t="s">
         <v>23</v>
@@ -4742,19 +4745,19 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F60" t="s">
         <v>20</v>
@@ -4762,19 +4765,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E61" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -4782,19 +4785,19 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C62" t="s">
         <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E62" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F62" t="s">
         <v>20</v>
@@ -4802,19 +4805,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
       </c>
       <c r="D63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E63" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
@@ -4822,39 +4825,39 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B64" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E64" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E65" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F65" t="s">
         <v>23</v>
@@ -4862,19 +4865,19 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
       </c>
       <c r="D66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F66" t="s">
         <v>11</v>
@@ -4882,19 +4885,19 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F67" t="s">
         <v>11</v>
@@ -4902,19 +4905,19 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C68" t="s">
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F68" t="s">
         <v>8</v>
@@ -4922,19 +4925,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E69" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F69" t="s">
         <v>20</v>
@@ -4942,19 +4945,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C70" t="s">
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E70" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F70" t="s">
         <v>23</v>
@@ -4962,19 +4965,19 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B71" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F71" t="s">
         <v>8</v>
@@ -4982,19 +4985,19 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F72" t="s">
         <v>23</v>
@@ -5002,19 +5005,19 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E73" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F73" t="s">
         <v>8</v>
@@ -5022,19 +5025,19 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B74" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C74" t="s">
         <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F74" t="s">
         <v>20</v>
@@ -5042,19 +5045,19 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C75" t="s">
         <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F75" t="s">
         <v>23</v>
@@ -5062,19 +5065,19 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C76" t="s">
         <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E76" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F76" t="s">
         <v>8</v>
@@ -5082,19 +5085,19 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B77" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E77" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F77" t="s">
         <v>23</v>
@@ -5102,19 +5105,19 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B78" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C78" t="s">
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E78" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F78" t="s">
         <v>8</v>
@@ -5122,19 +5125,19 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B79" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
       </c>
       <c r="D79" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F79" t="s">
         <v>11</v>
@@ -5142,19 +5145,19 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B80" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C80" t="s">
         <v>23</v>
       </c>
       <c r="D80" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E80" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F80" t="s">
         <v>23</v>
@@ -5162,19 +5165,19 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B81" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E81" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F81" t="s">
         <v>11</v>
@@ -5182,19 +5185,19 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B82" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E82" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F82" t="s">
         <v>11</v>
@@ -5202,19 +5205,19 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B83" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C83" t="s">
         <v>11</v>
       </c>
       <c r="D83" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E83" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F83" t="s">
         <v>23</v>
@@ -5222,19 +5225,19 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B84" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C84" t="s">
         <v>23</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E84" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F84" t="s">
         <v>20</v>
@@ -5242,19 +5245,19 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C85" t="s">
         <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F85" t="s">
         <v>20</v>
@@ -5262,19 +5265,19 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B86" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F86" t="s">
         <v>8</v>
@@ -5282,19 +5285,19 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C87" t="s">
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E87" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F87" t="s">
         <v>23</v>
@@ -5302,19 +5305,19 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B88" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C88" t="s">
         <v>23</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E88" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F88" t="s">
         <v>11</v>
@@ -5322,19 +5325,19 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B89" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C89" t="s">
         <v>23</v>
       </c>
       <c r="D89" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E89" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F89" t="s">
         <v>23</v>
@@ -5342,19 +5345,19 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B90" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C90" t="s">
         <v>23</v>
       </c>
       <c r="D90" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E90" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
@@ -5362,19 +5365,19 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B91" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C91" t="s">
         <v>8</v>
       </c>
       <c r="D91" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E91" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F91" t="s">
         <v>8</v>
@@ -5382,19 +5385,19 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B92" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E92" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F92" t="s">
         <v>20</v>
@@ -5402,19 +5405,19 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B93" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C93" t="s">
         <v>11</v>
       </c>
       <c r="D93" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E93" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F93" t="s">
         <v>20</v>
@@ -5422,19 +5425,19 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B94" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E94" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F94" t="s">
         <v>11</v>
@@ -5442,19 +5445,19 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B95" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C95" t="s">
         <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E95" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
@@ -5462,19 +5465,19 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B96" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C96" t="s">
         <v>8</v>
       </c>
       <c r="D96" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E96" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F96" t="s">
         <v>11</v>
@@ -5482,19 +5485,19 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B97" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C97" t="s">
         <v>23</v>
       </c>
       <c r="D97" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E97" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F97" t="s">
         <v>11</v>
@@ -5502,19 +5505,19 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B98" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
       </c>
       <c r="D98" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E98" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F98" t="s">
         <v>23</v>
@@ -5522,19 +5525,19 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B99" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C99" t="s">
         <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E99" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F99" t="s">
         <v>11</v>
@@ -5542,19 +5545,19 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B100" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C100" t="s">
         <v>8</v>
       </c>
       <c r="D100" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E100" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F100" t="s">
         <v>20</v>
@@ -5562,19 +5565,19 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B101" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C101" t="s">
         <v>23</v>
       </c>
       <c r="D101" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E101" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F101" t="s">
         <v>11</v>
@@ -5582,19 +5585,19 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B102" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E102" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F102" t="s">
         <v>8</v>
@@ -5602,19 +5605,19 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B103" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E103" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -5622,19 +5625,19 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B104" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C104" t="s">
         <v>23</v>
       </c>
       <c r="D104" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E104" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
@@ -5642,19 +5645,19 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B105" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
       </c>
       <c r="D105" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E105" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -5662,19 +5665,19 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B106" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C106" t="s">
         <v>8</v>
       </c>
       <c r="D106" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E106" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
@@ -5682,19 +5685,19 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B107" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C107" t="s">
         <v>23</v>
       </c>
       <c r="D107" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E107" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F107" t="s">
         <v>23</v>
@@ -5702,19 +5705,19 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B108" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C108" t="s">
         <v>23</v>
       </c>
       <c r="D108" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E108" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
@@ -5722,19 +5725,19 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B109" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E109" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F109" t="s">
         <v>11</v>
@@ -5742,19 +5745,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B110" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E110" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F110" t="s">
         <v>20</v>
@@ -5762,19 +5765,19 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B111" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C111" t="s">
         <v>8</v>
       </c>
       <c r="D111" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E111" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F111" t="s">
         <v>8</v>
@@ -5782,19 +5785,19 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B112" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C112" t="s">
         <v>23</v>
       </c>
       <c r="D112" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E112" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -5802,19 +5805,19 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B113" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C113" t="s">
         <v>23</v>
       </c>
       <c r="D113" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E113" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F113" t="s">
         <v>23</v>
@@ -5822,19 +5825,19 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B114" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E114" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F114" t="s">
         <v>20</v>
@@ -5842,19 +5845,19 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B115" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C115" t="s">
         <v>8</v>
       </c>
       <c r="D115" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E115" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F115" t="s">
         <v>23</v>
@@ -5862,19 +5865,19 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B116" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C116" t="s">
         <v>8</v>
       </c>
       <c r="D116" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E116" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F116" t="s">
         <v>23</v>
@@ -5882,19 +5885,19 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B117" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C117" t="s">
         <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E117" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
@@ -5902,19 +5905,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B118" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E118" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F118" t="s">
         <v>20</v>
@@ -5922,19 +5925,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B119" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C119" t="s">
         <v>11</v>
       </c>
       <c r="D119" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E119" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F119" t="s">
         <v>11</v>
@@ -5942,19 +5945,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B120" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C120" t="s">
         <v>11</v>
       </c>
       <c r="D120" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E120" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F120" t="s">
         <v>20</v>
@@ -5962,19 +5965,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B121" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E121" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F121" t="s">
         <v>11</v>
@@ -5982,19 +5985,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B122" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C122" t="s">
         <v>23</v>
       </c>
       <c r="D122" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E122" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F122" t="s">
         <v>23</v>
@@ -6002,19 +6005,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B123" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C123" t="s">
         <v>11</v>
       </c>
       <c r="D123" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E123" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F123" t="s">
         <v>11</v>
@@ -6022,19 +6025,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B124" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C124" t="s">
         <v>23</v>
       </c>
       <c r="D124" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E124" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F124" t="s">
         <v>23</v>
@@ -6042,19 +6045,19 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B125" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
       </c>
       <c r="D125" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E125" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F125" t="s">
         <v>11</v>
@@ -6062,19 +6065,19 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B126" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C126" t="s">
         <v>20</v>
       </c>
       <c r="D126" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E126" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F126" t="s">
         <v>23</v>
@@ -6082,39 +6085,39 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B127" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C127" t="s">
         <v>11</v>
       </c>
       <c r="D127" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E127" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F127" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B128" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E128" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F128" t="s">
         <v>23</v>
@@ -6122,39 +6125,39 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B129" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E129" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F129" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B130" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C130" t="s">
         <v>8</v>
       </c>
       <c r="D130" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E130" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F130" t="s">
         <v>11</v>
@@ -6162,19 +6165,19 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B131" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C131" t="s">
         <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E131" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F131" t="s">
         <v>11</v>
@@ -6182,19 +6185,19 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B132" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C132" t="s">
         <v>8</v>
       </c>
       <c r="D132" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E132" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F132" t="s">
         <v>11</v>
@@ -6202,19 +6205,19 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B133" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C133" t="s">
         <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E133" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F133" t="s">
         <v>20</v>
@@ -6222,19 +6225,19 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B134" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C134" t="s">
         <v>8</v>
       </c>
       <c r="D134" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E134" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F134" t="s">
         <v>8</v>
@@ -6242,19 +6245,19 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B135" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C135" t="s">
         <v>23</v>
       </c>
       <c r="D135" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E135" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -6262,19 +6265,19 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B136" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E136" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F136" t="s">
         <v>23</v>
